--- a/04_Features/modules/preservation/c_data/preservation_balanced.xlsx
+++ b/04_Features/modules/preservation/c_data/preservation_balanced.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">draw</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tan</t>
   </si>
   <si>
     <t xml:space="preserve">turquoise</t>
@@ -475,13 +478,13 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F2" t="n">
-        <v>6.72167747270293</v>
+        <v>17.4205160747565</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -498,13 +501,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="F3" t="n">
-        <v>20.2244345109165</v>
+        <v>15.0687790345946</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -521,13 +524,13 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7233148058549</v>
+        <v>15.6488714429374</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -544,13 +547,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8359156946095</v>
+        <v>10.3880818161213</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -567,13 +570,13 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0489561898201</v>
+        <v>11.0381737301404</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -590,13 +593,13 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>15.8809957081872</v>
+        <v>10.0476425496682</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -613,13 +616,13 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>8.37080659968002</v>
+        <v>15.3837671796906</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -636,13 +639,13 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>10.2408960111161</v>
+        <v>9.36521406494217</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -659,13 +662,13 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>14.1449336972158</v>
+        <v>9.80903978051135</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -682,13 +685,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>361</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>34.536937653962</v>
+        <v>5.90047341407261</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -705,13 +708,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1934021365134</v>
+        <v>34.332939602242</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -719,22 +722,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="F13" t="n">
-        <v>14.8809309754841</v>
+        <v>10.529644008235</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +751,16 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>14.1627541977334</v>
+        <v>20.9900341661381</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -771,16 +774,16 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>174</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13.6799033614756</v>
+      </c>
+      <c r="G15" t="n">
         <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>170</v>
-      </c>
-      <c r="F15" t="n">
-        <v>19.3465980384585</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -794,16 +797,16 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
-        <v>12.2402463617052</v>
+        <v>17.4160351926252</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -817,13 +820,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="F17" t="n">
-        <v>10.5255173295278</v>
+        <v>14.950619186453</v>
       </c>
       <c r="G17" t="n">
         <v>10</v>
@@ -840,16 +843,16 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>18.0301587087094</v>
+        <v>5.00753656216072</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -863,16 +866,16 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>11.9505535756512</v>
+        <v>12.1370413327452</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -886,16 +889,16 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>14.835946483991</v>
+        <v>18.0166087297244</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -909,16 +912,16 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>23.687013160745</v>
+        <v>11.5031012532519</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -932,16 +935,16 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>361</v>
+        <v>143</v>
       </c>
       <c r="F22" t="n">
-        <v>32.4570017067133</v>
+        <v>13.9572246956288</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -955,59 +958,59 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>13.3492148348464</v>
+        <v>12.0395328136042</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="F24" t="n">
-        <v>6.43309875149727</v>
+        <v>31.2032786257097</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="F25" t="n">
-        <v>14.8828178680067</v>
+        <v>20.5770343181675</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
@@ -1024,16 +1027,16 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>134</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.07066540092544</v>
+      </c>
+      <c r="G26" t="n">
         <v>11</v>
-      </c>
-      <c r="E26" t="n">
-        <v>170</v>
-      </c>
-      <c r="F26" t="n">
-        <v>9.0370370965447</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -1047,16 +1050,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="F27" t="n">
-        <v>11.8114804906407</v>
+        <v>15.9484275482183</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1070,16 +1073,16 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F28" t="n">
-        <v>6.90146023552522</v>
+        <v>11.4060540293228</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1093,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="F29" t="n">
-        <v>17.6668640960474</v>
+        <v>6.67783692569266</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -1116,16 +1119,16 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F30" t="n">
-        <v>9.09117332596054</v>
+        <v>10.3445039599523</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1139,16 +1142,16 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F31" t="n">
-        <v>6.22336719969626</v>
+        <v>9.9106024202814</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1162,16 +1165,16 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F32" t="n">
-        <v>3.38806851629987</v>
+        <v>17.2315025257016</v>
       </c>
       <c r="G32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1185,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>361</v>
+        <v>68</v>
       </c>
       <c r="F33" t="n">
-        <v>30.3120843997742</v>
+        <v>8.40667969389767</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1208,16 +1211,16 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F34" t="n">
-        <v>15.1000787527226</v>
+        <v>9.6728691562629</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1225,22 +1228,22 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="F35" t="n">
-        <v>17.1618525710338</v>
+        <v>6.56424977490375</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1251,22 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>211</v>
+        <v>359</v>
       </c>
       <c r="F36" t="n">
-        <v>12.6713306192167</v>
+        <v>31.0632232081055</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1271,22 +1274,22 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F37" t="n">
-        <v>18.5725152185626</v>
+        <v>10.6116537857644</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -1300,16 +1303,16 @@
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
         <v>134</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5467744037751</v>
+        <v>18.0234240186483</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1323,16 +1326,16 @@
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="F39" t="n">
-        <v>11.475232508571</v>
+        <v>13.9850343141044</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1346,16 +1349,16 @@
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="F40" t="n">
-        <v>18.1189791287178</v>
+        <v>16.0684226876334</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1369,16 +1372,16 @@
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="F41" t="n">
-        <v>11.84315841974</v>
+        <v>13.1992197544757</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -1392,16 +1395,16 @@
         <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F42" t="n">
-        <v>13.6058958508553</v>
+        <v>5.00149800818305</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1415,16 +1418,16 @@
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="F43" t="n">
-        <v>12.3372098816373</v>
+        <v>12.0027687910296</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -1438,16 +1441,16 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E44" t="n">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="F44" t="n">
-        <v>31.7519918405064</v>
+        <v>18.0304850110431</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1461,108 +1464,108 @@
         <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="F45" t="n">
-        <v>13.6884966764704</v>
+        <v>11.076240374465</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" t="n">
+        <v>143</v>
+      </c>
+      <c r="F46" t="n">
+        <v>13.769774510631</v>
+      </c>
+      <c r="G46" t="n">
         <v>9</v>
-      </c>
-      <c r="E46" t="n">
-        <v>103</v>
-      </c>
-      <c r="F46" t="n">
-        <v>6.9818660155621</v>
-      </c>
-      <c r="G46" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>10.6471097573203</v>
+        <v>12.0562838623789</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="F48" t="n">
-        <v>5.97327387910387</v>
+        <v>30.452652433182</v>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="F49" t="n">
-        <v>7.98299775154791</v>
+        <v>19.9869846837652</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1576,16 +1579,16 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="F50" t="n">
-        <v>8.6158999653665</v>
+        <v>7.90689248987738</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1599,16 +1602,16 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F51" t="n">
-        <v>22.1285545092949</v>
+        <v>7.34475696851703</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -1622,16 +1625,16 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="F52" t="n">
-        <v>8.16640829765896</v>
+        <v>7.65038504900731</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -1645,16 +1648,16 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="F53" t="n">
-        <v>6.40379901373359</v>
+        <v>5.47722833153921</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -1668,16 +1671,16 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E54" t="n">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="F54" t="n">
-        <v>4.10166590982939</v>
+        <v>5.92593083922165</v>
       </c>
       <c r="G54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1691,16 +1694,16 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E55" t="n">
-        <v>361</v>
+        <v>76</v>
       </c>
       <c r="F55" t="n">
-        <v>31.3011746664509</v>
+        <v>8.50007689508938</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -1714,16 +1717,16 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="F56" t="n">
-        <v>6.62238884584685</v>
+        <v>22.1206602530813</v>
       </c>
       <c r="G56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1731,22 +1734,22 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="F57" t="n">
-        <v>17.3217715755431</v>
+        <v>7.97100871789615</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -1754,22 +1757,22 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E58" t="n">
-        <v>211</v>
+        <v>143</v>
       </c>
       <c r="F58" t="n">
-        <v>11.5405567258155</v>
+        <v>6.85568424640018</v>
       </c>
       <c r="G58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -1777,22 +1780,22 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="F59" t="n">
-        <v>15.9605674342235</v>
+        <v>8.35964051261245</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -1800,22 +1803,22 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E60" t="n">
-        <v>134</v>
+        <v>359</v>
       </c>
       <c r="F60" t="n">
-        <v>13.1451244156518</v>
+        <v>33.1486302147602</v>
       </c>
       <c r="G60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1823,22 +1826,22 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5485181841505</v>
+        <v>10.3477205495461</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -1852,16 +1855,16 @@
         <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="F62" t="n">
-        <v>18.1078934210405</v>
+        <v>17.4450090711249</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -1875,16 +1878,16 @@
         <v>7</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F63" t="n">
-        <v>10.9797803855458</v>
+        <v>10.7325509784033</v>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -1898,16 +1901,16 @@
         <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="F64" t="n">
-        <v>13.1176063231636</v>
+        <v>13.316069433226</v>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -1921,16 +1924,16 @@
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E65" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="F65" t="n">
-        <v>13.3241519344429</v>
+        <v>11.884948373739</v>
       </c>
       <c r="G65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -1944,16 +1947,16 @@
         <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E66" t="n">
-        <v>361</v>
+        <v>63</v>
       </c>
       <c r="F66" t="n">
-        <v>31.7422205518614</v>
+        <v>4.68556570660785</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -1967,154 +1970,154 @@
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="F67" t="n">
-        <v>10.8721219767159</v>
+        <v>11.0966611924294</v>
       </c>
       <c r="G67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E68" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="F68" t="n">
-        <v>6.10166851570621</v>
+        <v>18.1511420892236</v>
       </c>
       <c r="G68" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>211</v>
+        <v>68</v>
       </c>
       <c r="F69" t="n">
-        <v>17.3586459242852</v>
+        <v>11.1763067084041</v>
       </c>
       <c r="G69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="F70" t="n">
-        <v>11.7818561978926</v>
+        <v>14.7063115170638</v>
       </c>
       <c r="G70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E71" t="n">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F71" t="n">
-        <v>12.6872534790242</v>
+        <v>12.3982761920388</v>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E72" t="n">
-        <v>69</v>
+        <v>359</v>
       </c>
       <c r="F72" t="n">
-        <v>6.6875166438371</v>
+        <v>30.3959030833666</v>
       </c>
       <c r="G72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E73" t="n">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="F73" t="n">
-        <v>18.7728166438707</v>
+        <v>20.6267500471674</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2128,16 +2131,16 @@
         <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F74" t="n">
-        <v>10.7757949804314</v>
+        <v>16.3136693466927</v>
       </c>
       <c r="G74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -2151,13 +2154,13 @@
         <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F75" t="n">
-        <v>10.1819291802725</v>
+        <v>15.6310471345871</v>
       </c>
       <c r="G75" t="n">
         <v>6</v>
@@ -2174,16 +2177,16 @@
         <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E76" t="n">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="F76" t="n">
-        <v>14.0730487191298</v>
+        <v>13.6182972227717</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2197,16 +2200,16 @@
         <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="F77" t="n">
-        <v>33.5783593006926</v>
+        <v>10.4519389191413</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -2220,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="F78" t="n">
-        <v>15.3027529525154</v>
+        <v>11.4424436817875</v>
       </c>
       <c r="G78" t="n">
         <v>5</v>
@@ -2237,22 +2240,22 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E79" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F79" t="n">
-        <v>14.1929512371326</v>
+        <v>13.3720759660848</v>
       </c>
       <c r="G79" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -2260,22 +2263,22 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E80" t="n">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="F80" t="n">
-        <v>14.1279805493339</v>
+        <v>17.9597975790388</v>
       </c>
       <c r="G80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2283,19 +2286,19 @@
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D81" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E81" t="n">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="F81" t="n">
-        <v>18.7645451770124</v>
+        <v>9.54474460601082</v>
       </c>
       <c r="G81" t="n">
         <v>7</v>
@@ -2306,19 +2309,19 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E82" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F82" t="n">
-        <v>12.352120767521</v>
+        <v>11.0490478181101</v>
       </c>
       <c r="G82" t="n">
         <v>9</v>
@@ -2329,22 +2332,22 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E83" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F83" t="n">
-        <v>11.6168398083908</v>
+        <v>6.34224756640732</v>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
@@ -2352,22 +2355,22 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E84" t="n">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="F84" t="n">
-        <v>17.528427820401</v>
+        <v>34.070345400547</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2375,22 +2378,22 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E85" t="n">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3457417261298</v>
+        <v>9.57344623943881</v>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -2404,16 +2407,16 @@
         <v>7</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="F86" t="n">
-        <v>14.1521948817159</v>
+        <v>21.6065930963745</v>
       </c>
       <c r="G86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2427,16 +2430,16 @@
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E87" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="F87" t="n">
-        <v>23.9747654465232</v>
+        <v>12.8394760148054</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -2450,16 +2453,16 @@
         <v>7</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E88" t="n">
-        <v>361</v>
+        <v>164</v>
       </c>
       <c r="F88" t="n">
-        <v>32.0637041780973</v>
+        <v>17.360160859119</v>
       </c>
       <c r="G88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2473,200 +2476,200 @@
         <v>7</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E89" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F89" t="n">
-        <v>12.5897359249601</v>
+        <v>15.0633516389174</v>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E90" t="n">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="F90" t="n">
-        <v>7.10327272973767</v>
+        <v>4.91753559653703</v>
       </c>
       <c r="G90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E91" t="n">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="F91" t="n">
-        <v>17.1785564025875</v>
+        <v>12.6292803648882</v>
       </c>
       <c r="G91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E92" t="n">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="F92" t="n">
-        <v>10.2023875942826</v>
+        <v>18.0978403471455</v>
       </c>
       <c r="G92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="F93" t="n">
-        <v>7.70216911934881</v>
+        <v>10.987694285891</v>
       </c>
       <c r="G93" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="F94" t="n">
-        <v>7.40785743855976</v>
+        <v>14.4425863191027</v>
       </c>
       <c r="G94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E95" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F95" t="n">
-        <v>18.0904150818467</v>
+        <v>12.1645142133022</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
-        <v>88</v>
+        <v>359</v>
       </c>
       <c r="F96" t="n">
-        <v>6.6815159723803</v>
+        <v>31.006763143171</v>
       </c>
       <c r="G96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="F97" t="n">
-        <v>10.08912052347</v>
+        <v>19.7665369630199</v>
       </c>
       <c r="G97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -2680,13 +2683,13 @@
         <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E98" t="n">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F98" t="n">
-        <v>14.5727881227008</v>
+        <v>17.641310732356</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
@@ -2703,16 +2706,16 @@
         <v>8</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E99" t="n">
-        <v>361</v>
+        <v>174</v>
       </c>
       <c r="F99" t="n">
-        <v>33.5077024907108</v>
+        <v>7.04006140549819</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
@@ -2726,16 +2729,16 @@
         <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E100" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F100" t="n">
-        <v>7.09571820599531</v>
+        <v>13.8417546109514</v>
       </c>
       <c r="G100" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -2743,22 +2746,22 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" t="n">
+        <v>156</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9.78692972459325</v>
+      </c>
+      <c r="G101" t="n">
         <v>9</v>
-      </c>
-      <c r="E101" t="n">
-        <v>103</v>
-      </c>
-      <c r="F101" t="n">
-        <v>15.8501109677474</v>
-      </c>
-      <c r="G101" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -2766,22 +2769,22 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="n">
+        <v>63</v>
+      </c>
+      <c r="F102" t="n">
+        <v>6.01837800304817</v>
+      </c>
+      <c r="G102" t="n">
         <v>10</v>
-      </c>
-      <c r="E102" t="n">
-        <v>211</v>
-      </c>
-      <c r="F102" t="n">
-        <v>13.9003827670398</v>
-      </c>
-      <c r="G102" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -2789,19 +2792,19 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D103" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="F103" t="n">
-        <v>17.9641758469488</v>
+        <v>7.87379325681156</v>
       </c>
       <c r="G103" t="n">
         <v>8</v>
@@ -2812,22 +2815,22 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D104" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="F104" t="n">
-        <v>12.5073533074313</v>
+        <v>18.1864285272031</v>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2835,19 +2838,19 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F105" t="n">
-        <v>12.4457623932988</v>
+        <v>9.76060133353843</v>
       </c>
       <c r="G105" t="n">
         <v>5</v>
@@ -2858,22 +2861,22 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D106" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="F106" t="n">
-        <v>17.790568681843</v>
+        <v>6.94655351608761</v>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
@@ -2881,22 +2884,22 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E107" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F107" t="n">
-        <v>10.5886380547844</v>
+        <v>6.96150865114375</v>
       </c>
       <c r="G107" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
@@ -2904,22 +2907,22 @@
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E108" t="n">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="F108" t="n">
-        <v>14.1516163044104</v>
+        <v>33.2759428678946</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -2927,22 +2930,22 @@
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D109" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E109" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="F109" t="n">
-        <v>23.7624763382326</v>
+        <v>10.726431686527</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110">
@@ -2956,16 +2959,16 @@
         <v>7</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E110" t="n">
-        <v>361</v>
+        <v>134</v>
       </c>
       <c r="F110" t="n">
-        <v>32.4393740983363</v>
+        <v>20.9647718438362</v>
       </c>
       <c r="G110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -2979,16 +2982,246 @@
         <v>7</v>
       </c>
       <c r="D111" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" t="n">
+        <v>174</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10.4250504830564</v>
+      </c>
+      <c r="G111" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="n">
+        <v>164</v>
+      </c>
+      <c r="F112" t="n">
+        <v>16.5635968853995</v>
+      </c>
+      <c r="G112" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" t="n">
+        <v>156</v>
+      </c>
+      <c r="F113" t="n">
+        <v>14.2913384465493</v>
+      </c>
+      <c r="G113" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="n">
+        <v>63</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.69133192197506</v>
+      </c>
+      <c r="G114" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" t="n">
+        <v>76</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11.1608725223391</v>
+      </c>
+      <c r="G115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" t="n">
+        <v>81</v>
+      </c>
+      <c r="F116" t="n">
+        <v>18.1712697885875</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="n">
+        <v>68</v>
+      </c>
+      <c r="F117" t="n">
+        <v>11.486801552512</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" t="n">
+        <v>143</v>
+      </c>
+      <c r="F118" t="n">
+        <v>14.2186288406542</v>
+      </c>
+      <c r="G118" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" t="n">
+        <v>58</v>
+      </c>
+      <c r="F119" t="n">
+        <v>11.8305406269169</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
         <v>19</v>
       </c>
-      <c r="E111" t="n">
-        <v>165</v>
-      </c>
-      <c r="F111" t="n">
-        <v>10.6017521931972</v>
-      </c>
-      <c r="G111" t="n">
-        <v>11</v>
+      <c r="E120" t="n">
+        <v>359</v>
+      </c>
+      <c r="F120" t="n">
+        <v>31.3111893412196</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" t="n">
+        <v>159</v>
+      </c>
+      <c r="F121" t="n">
+        <v>21.4627534912527</v>
+      </c>
+      <c r="G121" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3007,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -3015,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -3023,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -3031,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -3039,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -3047,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -3055,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -3063,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -3071,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -3079,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -3087,7 +3320,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -3095,7 +3328,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -3103,7 +3336,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -3111,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -3119,7 +3352,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -3127,7 +3360,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -3135,7 +3368,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -3143,7 +3376,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -3151,7 +3384,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -3159,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -3167,7 +3400,7 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -3175,7 +3408,7 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -3183,7 +3416,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -3191,7 +3424,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -3199,7 +3432,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -3207,7 +3440,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -3215,7 +3448,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -3223,7 +3456,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -3231,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -3239,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -3247,7 +3480,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3266,13 +3499,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
